--- a/blendmaster_backend_OOP/output/outcome_data.xlsx
+++ b/blendmaster_backend_OOP/output/outcome_data.xlsx
@@ -1,40 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlendMaster\blendmaster_backend_OOP\output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435512C2-8D74-40FF-B8C5-F36C8994AE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="19">
+  <si>
+    <t>start_datetime</t>
+  </si>
+  <si>
+    <t>end_datetime</t>
+  </si>
+  <si>
+    <t>steady_state_duration</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>opening_balance</t>
+  </si>
+  <si>
+    <t>actual_tonnes</t>
+  </si>
+  <si>
+    <t>remaining_tonnes</t>
+  </si>
+  <si>
+    <t>grade_fe</t>
+  </si>
+  <si>
+    <t>equipment</t>
+  </si>
+  <si>
+    <t>equipment_rate_input</t>
+  </si>
+  <si>
+    <t>equipment_rate_output</t>
+  </si>
+  <si>
+    <t>preplan</t>
+  </si>
+  <si>
+    <t>SP1</t>
+  </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>GB2</t>
+  </si>
+  <si>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>period_1</t>
+  </si>
+  <si>
+    <t>period_2</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +117,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,14 +443,518 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>45601.985905899339</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45602.25</v>
+      </c>
+      <c r="C2">
+        <v>6.3382584158333328</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <v>20000</v>
+      </c>
+      <c r="G2">
+        <v>12676.51683166667</v>
+      </c>
+      <c r="H2">
+        <v>7323.4831683333341</v>
+      </c>
+      <c r="I2">
+        <v>57</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2">
+        <v>3000</v>
+      </c>
+      <c r="L2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>45601.985905899339</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45602.25</v>
+      </c>
+      <c r="C3">
+        <v>6.3382584158333328</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <v>20000</v>
+      </c>
+      <c r="G3">
+        <v>6338.258415833332</v>
+      </c>
+      <c r="H3">
+        <v>13661.74158416667</v>
+      </c>
+      <c r="I3">
+        <v>60</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3">
+        <v>3000</v>
+      </c>
+      <c r="L3">
+        <v>999.99999999999989</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>45601.985905899339</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45602.087620943348</v>
+      </c>
+      <c r="C4">
+        <v>2.441161056111111</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>7323.4831683333341</v>
+      </c>
+      <c r="G4">
+        <v>4882.322112222223</v>
+      </c>
+      <c r="H4">
+        <v>2441.1610561111111</v>
+      </c>
+      <c r="I4">
+        <v>57</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4">
+        <v>3000</v>
+      </c>
+      <c r="L4">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>45601.985905899339</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45602.087620943348</v>
+      </c>
+      <c r="C5">
+        <v>2.441161056111111</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <v>13661.74158416667</v>
+      </c>
+      <c r="G5">
+        <v>2441.1610561111111</v>
+      </c>
+      <c r="H5">
+        <v>11220.58052805556</v>
+      </c>
+      <c r="I5">
+        <v>60</v>
+      </c>
+      <c r="J5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5">
+        <v>3000</v>
+      </c>
+      <c r="L5">
+        <v>999.99999999999989</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>45602.25</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45602.283905014658</v>
+      </c>
+      <c r="C6">
+        <v>0.81372035203703708</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>2441.1610561111111</v>
+      </c>
+      <c r="G6">
+        <v>1627.4407040740739</v>
+      </c>
+      <c r="H6">
+        <v>813.72035203703695</v>
+      </c>
+      <c r="I6">
+        <v>57</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6">
+        <v>3000</v>
+      </c>
+      <c r="L6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>45602.25</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45602.283905014658</v>
+      </c>
+      <c r="C7">
+        <v>0.81372035203703708</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>11220.58052805556</v>
+      </c>
+      <c r="G7">
+        <v>813.72035203703695</v>
+      </c>
+      <c r="H7">
+        <v>10406.860176018519</v>
+      </c>
+      <c r="I7">
+        <v>60</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7">
+        <v>3000</v>
+      </c>
+      <c r="L7">
+        <v>999.99999999999989</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>45602.25</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45602.261301671548</v>
+      </c>
+      <c r="C8">
+        <v>0.27124011734567899</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>813.72035203703695</v>
+      </c>
+      <c r="G8">
+        <v>542.48023469135796</v>
+      </c>
+      <c r="H8">
+        <v>271.24011734567898</v>
+      </c>
+      <c r="I8">
+        <v>57</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8">
+        <v>3000</v>
+      </c>
+      <c r="L8">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>45602.25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45602.261301671548</v>
+      </c>
+      <c r="C9">
+        <v>0.27124011734567899</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9">
+        <v>10406.860176018519</v>
+      </c>
+      <c r="G9">
+        <v>271.24011734567898</v>
+      </c>
+      <c r="H9">
+        <v>10135.620058672839</v>
+      </c>
+      <c r="I9">
+        <v>60</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9">
+        <v>3000</v>
+      </c>
+      <c r="L9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>45602.75</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45602.753767223847</v>
+      </c>
+      <c r="C10">
+        <v>9.0413372448559667E-2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>271.24011734567898</v>
+      </c>
+      <c r="G10">
+        <v>180.82674489711931</v>
+      </c>
+      <c r="H10">
+        <v>90.41337244855967</v>
+      </c>
+      <c r="I10">
+        <v>57</v>
+      </c>
+      <c r="J10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10">
+        <v>3000</v>
+      </c>
+      <c r="L10">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>45602.75</v>
+      </c>
+      <c r="B11" s="2">
+        <v>45602.753767223847</v>
+      </c>
+      <c r="C11">
+        <v>9.0413372448559667E-2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11">
+        <v>10135.620058672839</v>
+      </c>
+      <c r="G11">
+        <v>90.41337244855967</v>
+      </c>
+      <c r="H11">
+        <v>10045.206686224279</v>
+      </c>
+      <c r="I11">
+        <v>60</v>
+      </c>
+      <c r="J11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11">
+        <v>3000</v>
+      </c>
+      <c r="L11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>45602.75</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45602.751255741277</v>
+      </c>
+      <c r="C12">
+        <v>3.013779081618656E-2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <v>90.41337244855967</v>
+      </c>
+      <c r="G12">
+        <v>60.275581632373111</v>
+      </c>
+      <c r="H12">
+        <v>30.137790816186559</v>
+      </c>
+      <c r="I12">
+        <v>57</v>
+      </c>
+      <c r="J12" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12">
+        <v>3000</v>
+      </c>
+      <c r="L12">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>45602.75</v>
+      </c>
+      <c r="B13" s="2">
+        <v>45602.751255741277</v>
+      </c>
+      <c r="C13">
+        <v>3.013779081618656E-2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13">
+        <v>10045.206686224279</v>
+      </c>
+      <c r="G13">
+        <v>30.137790816186559</v>
+      </c>
+      <c r="H13">
+        <v>10015.0688954081</v>
+      </c>
+      <c r="I13">
+        <v>60</v>
+      </c>
+      <c r="J13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13">
+        <v>3000</v>
+      </c>
+      <c r="L13">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/blendmaster_backend_OOP/output/outcome_data.xlsx
+++ b/blendmaster_backend_OOP/output/outcome_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlendMaster\blendmaster_backend_OOP\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435512C2-8D74-40FF-B8C5-F36C8994AE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416347B3-0D60-41E0-ACD4-0AFFD312C59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
   <si>
     <t>start_datetime</t>
   </si>
@@ -67,6 +67,9 @@
     <t>RC</t>
   </si>
   <si>
+    <t>SP2</t>
+  </si>
+  <si>
     <t>GB2</t>
   </si>
   <si>
@@ -76,7 +79,13 @@
     <t>period_1</t>
   </si>
   <si>
-    <t>period_2</t>
+    <t>SP3</t>
+  </si>
+  <si>
+    <t>GB1</t>
+  </si>
+  <si>
+    <t>SP4</t>
   </si>
 </sst>
 </file>
@@ -444,20 +453,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -500,13 +509,13 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>45601.985905899339</v>
+        <v>45602.604718243019</v>
       </c>
       <c r="B2" s="2">
-        <v>45602.25</v>
+        <v>45602.75</v>
       </c>
       <c r="C2">
-        <v>6.3382584158333328</v>
+        <v>3.4867621674999998</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -518,10 +527,10 @@
         <v>20000</v>
       </c>
       <c r="G2">
-        <v>12676.51683166667</v>
+        <v>10460.286502499999</v>
       </c>
       <c r="H2">
-        <v>7323.4831683333341</v>
+        <v>9539.7134975000008</v>
       </c>
       <c r="I2">
         <v>57</v>
@@ -533,18 +542,18 @@
         <v>3000</v>
       </c>
       <c r="L2">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>45601.985905899339</v>
+        <v>45602.604718243019</v>
       </c>
       <c r="B3" s="2">
-        <v>45602.25</v>
+        <v>45602.75</v>
       </c>
       <c r="C3">
-        <v>6.3382584158333328</v>
+        <v>3.4867621674999998</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -556,16 +565,16 @@
         <v>20000</v>
       </c>
       <c r="G3">
-        <v>6338.258415833332</v>
+        <v>3486.7621675</v>
       </c>
       <c r="H3">
-        <v>13661.74158416667</v>
+        <v>16513.237832499999</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K3">
         <v>3000</v>
@@ -576,34 +585,34 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>45601.985905899339</v>
+        <v>45602.604718243019</v>
       </c>
       <c r="B4" s="2">
-        <v>45602.087620943348</v>
+        <v>45602.75</v>
       </c>
       <c r="C4">
-        <v>2.441161056111111</v>
+        <v>3.4867621674999998</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>7323.4831683333341</v>
+        <v>20000</v>
       </c>
       <c r="G4">
-        <v>4882.322112222223</v>
+        <v>6973.5243350000001</v>
       </c>
       <c r="H4">
-        <v>2441.1610561111111</v>
+        <v>13026.475665</v>
       </c>
       <c r="I4">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K4">
         <v>3000</v>
@@ -614,66 +623,66 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>45601.985905899339</v>
+        <v>45602.604718243019</v>
       </c>
       <c r="B5" s="2">
-        <v>45602.087620943348</v>
+        <v>45602.73721426382</v>
       </c>
       <c r="C5">
-        <v>2.441161056111111</v>
+        <v>3.1799044991666672</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>13661.74158416667</v>
+        <v>9539.7134975000008</v>
       </c>
       <c r="G5">
-        <v>2441.1610561111111</v>
+        <v>9539.7134975000008</v>
       </c>
       <c r="H5">
-        <v>11220.58052805556</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K5">
         <v>3000</v>
       </c>
       <c r="L5">
-        <v>999.99999999999989</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>45602.25</v>
+        <v>45602.604718243019</v>
       </c>
       <c r="B6" s="2">
-        <v>45602.283905014658</v>
+        <v>45602.73721426382</v>
       </c>
       <c r="C6">
-        <v>0.81372035203703708</v>
+        <v>3.1799044991666672</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>2441.1610561111111</v>
+        <v>16513.237832499999</v>
       </c>
       <c r="G6">
-        <v>1627.4407040740739</v>
+        <v>3179.9044991666669</v>
       </c>
       <c r="H6">
-        <v>813.72035203703695</v>
+        <v>13333.33333333333</v>
       </c>
       <c r="I6">
         <v>57</v>
@@ -685,71 +694,71 @@
         <v>3000</v>
       </c>
       <c r="L6">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>45602.25</v>
+        <v>45602.604718243019</v>
       </c>
       <c r="B7" s="2">
-        <v>45602.283905014658</v>
+        <v>45602.73721426382</v>
       </c>
       <c r="C7">
-        <v>0.81372035203703708</v>
+        <v>3.1799044991666672</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>11220.58052805556</v>
+        <v>13026.475665</v>
       </c>
       <c r="G7">
-        <v>813.72035203703695</v>
+        <v>6359.8089983333339</v>
       </c>
       <c r="H7">
-        <v>10406.860176018519</v>
+        <v>6666.6666666666661</v>
       </c>
       <c r="I7">
         <v>60</v>
       </c>
       <c r="J7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7">
         <v>3000</v>
       </c>
       <c r="L7">
-        <v>999.99999999999989</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>45602.25</v>
+        <v>45602.75</v>
       </c>
       <c r="B8" s="2">
-        <v>45602.261301671548</v>
+        <v>45603.027777777781</v>
       </c>
       <c r="C8">
-        <v>0.27124011734567899</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>813.72035203703695</v>
+        <v>13333.33333333333</v>
       </c>
       <c r="G8">
-        <v>542.48023469135796</v>
+        <v>13333.33333333333</v>
       </c>
       <c r="H8">
-        <v>271.24011734567898</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>57</v>
@@ -766,40 +775,40 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>45602.25</v>
+        <v>45602.75</v>
       </c>
       <c r="B9" s="2">
-        <v>45602.261301671548</v>
+        <v>45603.027777777781</v>
       </c>
       <c r="C9">
-        <v>0.27124011734567899</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>10406.860176018519</v>
+        <v>20000</v>
       </c>
       <c r="G9">
-        <v>271.24011734567898</v>
+        <v>13333.33333333333</v>
       </c>
       <c r="H9">
-        <v>10135.620058672839</v>
+        <v>6666.6666666666661</v>
       </c>
       <c r="I9">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K9">
         <v>3000</v>
       </c>
       <c r="L9">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -807,37 +816,37 @@
         <v>45602.75</v>
       </c>
       <c r="B10" s="2">
-        <v>45602.753767223847</v>
+        <v>45603.027777777781</v>
       </c>
       <c r="C10">
-        <v>9.0413372448559667E-2</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>271.24011734567898</v>
+        <v>20000</v>
       </c>
       <c r="G10">
-        <v>180.82674489711931</v>
+        <v>6666.6666666666661</v>
       </c>
       <c r="H10">
-        <v>90.41337244855967</v>
+        <v>13333.33333333333</v>
       </c>
       <c r="I10">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K10">
         <v>3000</v>
       </c>
       <c r="L10">
-        <v>2000</v>
+        <v>999.99999999999989</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -845,37 +854,37 @@
         <v>45602.75</v>
       </c>
       <c r="B11" s="2">
-        <v>45602.753767223847</v>
+        <v>45603.027777777781</v>
       </c>
       <c r="C11">
-        <v>9.0413372448559667E-2</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>10135.620058672839</v>
+        <v>6666.6666666666661</v>
       </c>
       <c r="G11">
-        <v>90.41337244855967</v>
+        <v>6666.6666666666661</v>
       </c>
       <c r="H11">
-        <v>10045.206686224279</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>60</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11">
         <v>3000</v>
       </c>
       <c r="L11">
-        <v>1000</v>
+        <v>999.99999999999989</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -883,25 +892,25 @@
         <v>45602.75</v>
       </c>
       <c r="B12" s="2">
-        <v>45602.751255741277</v>
+        <v>45603.25</v>
       </c>
       <c r="C12">
-        <v>3.013779081618656E-2</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>90.41337244855967</v>
+        <v>6666.6666666666661</v>
       </c>
       <c r="G12">
-        <v>60.275581632373111</v>
+        <v>6666.6666666666661</v>
       </c>
       <c r="H12">
-        <v>30.137790816186559</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>57</v>
@@ -913,7 +922,7 @@
         <v>3000</v>
       </c>
       <c r="L12">
-        <v>2000</v>
+        <v>555.55555555555554</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -921,37 +930,75 @@
         <v>45602.75</v>
       </c>
       <c r="B13" s="2">
-        <v>45602.751255741277</v>
+        <v>45603.25</v>
       </c>
       <c r="C13">
-        <v>3.013779081618656E-2</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>10045.206686224279</v>
+        <v>20000</v>
       </c>
       <c r="G13">
-        <v>30.137790816186559</v>
+        <v>20000</v>
       </c>
       <c r="H13">
-        <v>10015.0688954081</v>
+        <v>0</v>
       </c>
       <c r="I13">
+        <v>57</v>
+      </c>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13">
+        <v>3000</v>
+      </c>
+      <c r="L13">
+        <v>1666.666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>45602.75</v>
+      </c>
+      <c r="B14" s="2">
+        <v>45603.25</v>
+      </c>
+      <c r="C14">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14">
+        <v>13333.33333333333</v>
+      </c>
+      <c r="G14">
+        <v>13333.33333333333</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>60</v>
       </c>
-      <c r="J13" t="s">
-        <v>16</v>
-      </c>
-      <c r="K13">
-        <v>3000</v>
-      </c>
-      <c r="L13">
-        <v>1000</v>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14">
+        <v>3000</v>
+      </c>
+      <c r="L14">
+        <v>1111.1111111111111</v>
       </c>
     </row>
   </sheetData>

--- a/blendmaster_backend_OOP/output/outcome_data.xlsx
+++ b/blendmaster_backend_OOP/output/outcome_data.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlendMaster\blendmaster_backend_OOP\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416347B3-0D60-41E0-ACD4-0AFFD312C59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED73ED3-9088-4BC6-A2C4-F70EAF2FE390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$19</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>start_datetime</t>
   </si>
@@ -61,31 +64,34 @@
     <t>preplan</t>
   </si>
   <si>
+    <t>SP4</t>
+  </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>GB2</t>
+  </si>
+  <si>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>period_1</t>
+  </si>
+  <si>
+    <t>SP3</t>
+  </si>
+  <si>
+    <t>GB1</t>
+  </si>
+  <si>
+    <t>period_2</t>
+  </si>
+  <si>
+    <t>SP2</t>
+  </si>
+  <si>
     <t>SP1</t>
-  </si>
-  <si>
-    <t>RC</t>
-  </si>
-  <si>
-    <t>SP2</t>
-  </si>
-  <si>
-    <t>GB2</t>
-  </si>
-  <si>
-    <t>EX</t>
-  </si>
-  <si>
-    <t>period_1</t>
-  </si>
-  <si>
-    <t>SP3</t>
-  </si>
-  <si>
-    <t>GB1</t>
-  </si>
-  <si>
-    <t>SP4</t>
   </si>
 </sst>
 </file>
@@ -453,12 +459,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L14"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" customWidth="1"/>
     <col min="5" max="5" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
@@ -507,15 +514,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>45602.604718243019</v>
+        <v>45604.109561397789</v>
       </c>
       <c r="B2" s="2">
-        <v>45602.75</v>
+        <v>45604.25</v>
       </c>
       <c r="C2">
-        <v>3.4867621674999998</v>
+        <v>3.3705264530555561</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -527,13 +534,13 @@
         <v>20000</v>
       </c>
       <c r="G2">
-        <v>10460.286502499999</v>
+        <v>8426.316132638889</v>
       </c>
       <c r="H2">
-        <v>9539.7134975000008</v>
+        <v>11573.683867361109</v>
       </c>
       <c r="I2">
-        <v>57</v>
+        <v>58.2</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -542,18 +549,18 @@
         <v>3000</v>
       </c>
       <c r="L2">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>45602.604718243019</v>
+        <v>45604.109561397789</v>
       </c>
       <c r="B3" s="2">
-        <v>45602.75</v>
+        <v>45604.25</v>
       </c>
       <c r="C3">
-        <v>3.4867621674999998</v>
+        <v>3.3705264530555561</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -562,92 +569,92 @@
         <v>15</v>
       </c>
       <c r="F3">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="G3">
-        <v>3486.7621675</v>
+        <v>1685.2632265277771</v>
       </c>
       <c r="H3">
-        <v>16513.237832499999</v>
+        <v>3314.7367734722229</v>
       </c>
       <c r="I3">
-        <v>57</v>
+        <v>60.2</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K3">
         <v>3000</v>
       </c>
       <c r="L3">
-        <v>999.99999999999989</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>499.99999999999977</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>45602.604718243019</v>
+        <v>45604.25</v>
       </c>
       <c r="B4" s="2">
-        <v>45602.75</v>
+        <v>45604.75</v>
       </c>
       <c r="C4">
-        <v>3.4867621674999998</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>20000</v>
       </c>
       <c r="G4">
-        <v>6973.5243350000001</v>
+        <v>18426.316132638891</v>
       </c>
       <c r="H4">
-        <v>13026.475665</v>
+        <v>1573.6838673611089</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>58.1</v>
       </c>
       <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4">
+        <v>3000</v>
+      </c>
+      <c r="L4">
+        <v>1535.526344386574</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>45604.25</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45604.75</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
-      </c>
-      <c r="K4">
-        <v>3000</v>
-      </c>
-      <c r="L4">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>45602.604718243019</v>
-      </c>
-      <c r="B5" s="2">
-        <v>45602.73721426382</v>
-      </c>
-      <c r="C5">
-        <v>3.1799044991666672</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5">
-        <v>9539.7134975000008</v>
+        <v>11573.683867361109</v>
       </c>
       <c r="G5">
-        <v>9539.7134975000008</v>
+        <v>11573.683867361109</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>57</v>
+        <v>58.2</v>
       </c>
       <c r="J5" t="s">
         <v>14</v>
@@ -656,302 +663,302 @@
         <v>3000</v>
       </c>
       <c r="L5">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>964.47365561342588</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>45602.604718243019</v>
+        <v>45604.25</v>
       </c>
       <c r="B6" s="2">
-        <v>45602.73721426382</v>
+        <v>45604.75</v>
       </c>
       <c r="C6">
-        <v>3.1799044991666672</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6">
+        <v>5000</v>
+      </c>
+      <c r="G6">
+        <v>2685.2632265277748</v>
+      </c>
+      <c r="H6">
+        <v>2314.7367734722252</v>
+      </c>
+      <c r="I6">
+        <v>60.5</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>3000</v>
+      </c>
+      <c r="L6">
+        <v>223.7719355439813</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>45604.25</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45604.75</v>
+      </c>
+      <c r="C7">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
         <v>15</v>
       </c>
-      <c r="F6">
-        <v>16513.237832499999</v>
-      </c>
-      <c r="G6">
-        <v>3179.9044991666669</v>
-      </c>
-      <c r="H6">
-        <v>13333.33333333333</v>
-      </c>
-      <c r="I6">
-        <v>57</v>
-      </c>
-      <c r="J6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6">
-        <v>3000</v>
-      </c>
-      <c r="L6">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>45602.604718243019</v>
-      </c>
-      <c r="B7" s="2">
-        <v>45602.73721426382</v>
-      </c>
-      <c r="C7">
-        <v>3.1799044991666672</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7">
+        <v>3314.7367734722229</v>
+      </c>
+      <c r="G7">
+        <v>3314.7367734722229</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>60.2</v>
+      </c>
+      <c r="J7" t="s">
         <v>16</v>
       </c>
-      <c r="F7">
-        <v>13026.475665</v>
-      </c>
-      <c r="G7">
-        <v>6359.8089983333339</v>
-      </c>
-      <c r="H7">
-        <v>6666.6666666666661</v>
-      </c>
-      <c r="I7">
-        <v>60</v>
-      </c>
-      <c r="J7" t="s">
-        <v>17</v>
-      </c>
       <c r="K7">
         <v>3000</v>
       </c>
       <c r="L7">
-        <v>2000</v>
+        <v>276.22806445601861</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>45602.75</v>
+        <v>45604.75</v>
       </c>
       <c r="B8" s="2">
-        <v>45603.027777777781</v>
+        <v>45604.771856720377</v>
       </c>
       <c r="C8">
-        <v>6.666666666666667</v>
+        <v>0.5245612891203697</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>13333.33333333333</v>
+        <v>2314.7367734722252</v>
       </c>
       <c r="G8">
-        <v>13333.33333333333</v>
+        <v>262.28064456018478</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2052.4561289120402</v>
       </c>
       <c r="I8">
-        <v>57</v>
+        <v>60.5</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K8">
         <v>3000</v>
       </c>
       <c r="L8">
-        <v>2000</v>
+        <v>499.99999999999989</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>45602.75</v>
+        <v>45604.771856720377</v>
       </c>
       <c r="B9" s="2">
-        <v>45603.027777777781</v>
+        <v>45604.775499507108</v>
       </c>
       <c r="C9">
-        <v>6.666666666666667</v>
+        <v>8.7426881520061589E-2</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
       </c>
       <c r="F9">
-        <v>20000</v>
+        <v>2052.4561289120402</v>
       </c>
       <c r="G9">
-        <v>13333.33333333333</v>
+        <v>43.713440760030807</v>
       </c>
       <c r="H9">
-        <v>6666.6666666666661</v>
+        <v>2008.7426881520089</v>
       </c>
       <c r="I9">
-        <v>57</v>
+        <v>60.5</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K9">
         <v>3000</v>
       </c>
       <c r="L9">
-        <v>2000</v>
+        <v>500.00000000000011</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>45602.75</v>
+        <v>45604.775499507108</v>
       </c>
       <c r="B10" s="2">
-        <v>45603.027777777781</v>
+        <v>45604.776193951562</v>
       </c>
       <c r="C10">
-        <v>6.666666666666667</v>
+        <v>1.6666667E-2</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>20000</v>
+        <v>2008.7426881520089</v>
       </c>
       <c r="G10">
-        <v>6666.6666666666661</v>
+        <v>8.3333335000000019</v>
       </c>
       <c r="H10">
-        <v>13333.33333333333</v>
+        <v>2000.4093546520089</v>
       </c>
       <c r="I10">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K10">
         <v>3000</v>
       </c>
       <c r="L10">
-        <v>999.99999999999989</v>
+        <v>500.00000000000011</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>45602.75</v>
+        <v>45604.776193951562</v>
       </c>
       <c r="B11" s="2">
-        <v>45603.027777777781</v>
+        <v>45604.776888396023</v>
       </c>
       <c r="C11">
-        <v>6.666666666666667</v>
+        <v>1.6666667E-2</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11">
+        <v>2000.4093546520089</v>
+      </c>
+      <c r="G11">
+        <v>8.3333335000000019</v>
+      </c>
+      <c r="H11">
+        <v>1992.0760211520089</v>
+      </c>
+      <c r="I11">
+        <v>60.5</v>
+      </c>
+      <c r="J11" t="s">
         <v>16</v>
       </c>
-      <c r="F11">
-        <v>6666.6666666666661</v>
-      </c>
-      <c r="G11">
-        <v>6666.6666666666661</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>60</v>
-      </c>
-      <c r="J11" t="s">
-        <v>17</v>
-      </c>
       <c r="K11">
         <v>3000</v>
       </c>
       <c r="L11">
-        <v>999.99999999999989</v>
+        <v>500.00000000000011</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>45602.75</v>
+        <v>45604.776888396023</v>
       </c>
       <c r="B12" s="2">
-        <v>45603.25</v>
+        <v>45605.054115897488</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>6.6534600352533442</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12">
-        <v>6666.6666666666661</v>
+        <v>1992.0760211520089</v>
       </c>
       <c r="G12">
-        <v>6666.6666666666661</v>
+        <v>1992.0760211520089</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>57</v>
+        <v>60.5</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K12">
         <v>3000</v>
       </c>
       <c r="L12">
-        <v>555.55555555555554</v>
+        <v>299.40452194752788</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>45602.75</v>
+        <v>45605.054115897488</v>
       </c>
       <c r="B13" s="2">
-        <v>45603.25</v>
+        <v>45605.25</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>4.7012184602777776</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13">
         <v>20000</v>
       </c>
       <c r="G13">
-        <v>20000</v>
+        <v>14103.65538083333</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>5896.3446191666681</v>
       </c>
       <c r="I13">
-        <v>57</v>
+        <v>58.4</v>
       </c>
       <c r="J13" t="s">
         <v>14</v>
@@ -960,48 +967,248 @@
         <v>3000</v>
       </c>
       <c r="L13">
-        <v>1666.666666666667</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>45602.75</v>
+        <v>45604.776193951562</v>
       </c>
       <c r="B14" s="2">
-        <v>45603.25</v>
+        <v>45604.776888396023</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>1.6666667E-2</v>
       </c>
       <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14">
+        <v>20000</v>
+      </c>
+      <c r="G14">
+        <v>39.619894239969177</v>
+      </c>
+      <c r="H14">
+        <v>19960.380105760029</v>
+      </c>
+      <c r="I14">
+        <v>58.1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14">
+        <v>3000</v>
+      </c>
+      <c r="L14">
+        <v>2377.1936068542791</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>45604.776888396023</v>
+      </c>
+      <c r="B15" s="2">
+        <v>45605.054115897488</v>
+      </c>
+      <c r="C15">
+        <v>6.6534600352533442</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15">
+        <v>19960.380105760029</v>
+      </c>
+      <c r="G15">
+        <v>17968.304084608018</v>
+      </c>
+      <c r="H15">
+        <v>1992.0760211520101</v>
+      </c>
+      <c r="I15">
+        <v>58.1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15">
+        <v>3000</v>
+      </c>
+      <c r="L15">
+        <v>2700.5954780524721</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>45604.75</v>
+      </c>
+      <c r="B16" s="2">
+        <v>45604.771856720377</v>
+      </c>
+      <c r="C16">
+        <v>0.5245612891203697</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
         <v>18</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F16">
+        <v>1573.6838673611089</v>
+      </c>
+      <c r="G16">
+        <v>1311.4032228009239</v>
+      </c>
+      <c r="H16">
+        <v>262.28064456018478</v>
+      </c>
+      <c r="I16">
+        <v>58.1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16">
+        <v>3000</v>
+      </c>
+      <c r="L16">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>45604.771856720377</v>
+      </c>
+      <c r="B17" s="2">
+        <v>45604.775499507108</v>
+      </c>
+      <c r="C17">
+        <v>8.7426881520061589E-2</v>
+      </c>
+      <c r="D17" t="s">
         <v>20</v>
       </c>
-      <c r="F14">
-        <v>13333.33333333333</v>
-      </c>
-      <c r="G14">
-        <v>13333.33333333333</v>
-      </c>
-      <c r="H14">
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17">
+        <v>262.28064456018478</v>
+      </c>
+      <c r="G17">
+        <v>218.567203800154</v>
+      </c>
+      <c r="H17">
+        <v>43.713440760030807</v>
+      </c>
+      <c r="I17">
+        <v>58.1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17">
+        <v>3000</v>
+      </c>
+      <c r="L17">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>45604.775499507108</v>
+      </c>
+      <c r="B18" s="2">
+        <v>45604.776193951562</v>
+      </c>
+      <c r="C18">
+        <v>1.6666667E-2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18">
+        <v>43.713440760030807</v>
+      </c>
+      <c r="G18">
+        <v>41.666667500000003</v>
+      </c>
+      <c r="H18">
+        <v>2.0467732600308111</v>
+      </c>
+      <c r="I18">
+        <v>58.1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18">
+        <v>3000</v>
+      </c>
+      <c r="L18">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>45604.776193951562</v>
+      </c>
+      <c r="B19" s="2">
+        <v>45604.776888396023</v>
+      </c>
+      <c r="C19">
+        <v>1.6666667E-2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19">
+        <v>2.0467732600308111</v>
+      </c>
+      <c r="G19">
+        <v>2.0467732600308111</v>
+      </c>
+      <c r="H19">
         <v>0</v>
       </c>
-      <c r="I14">
-        <v>60</v>
-      </c>
-      <c r="J14" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14">
-        <v>3000</v>
-      </c>
-      <c r="L14">
-        <v>1111.1111111111111</v>
+      <c r="I19">
+        <v>58.1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19">
+        <v>3000</v>
+      </c>
+      <c r="L19">
+        <v>122.8063931457208</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L19" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="period_2"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:L19">
+      <sortCondition ref="E1:E19"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>